--- a/MSK FETCH/msk_service_port_seq.xlsx
+++ b/MSK FETCH/msk_service_port_seq.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\demo\capaStudy\MSK FETCH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5F5974-3F33-4DB3-92D0-9D5E9ED8C049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E009586E-4808-496A-A69C-F9CDB20061F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5145" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{D81B5631-E93A-4C80-84BC-EACFC8E297C7}"/>
+    <workbookView xWindow="5130" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D81B5631-E93A-4C80-84BC-EACFC8E297C7}"/>
   </bookViews>
   <sheets>
     <sheet name="PortCalls" sheetId="2" r:id="rId1"/>

--- a/MSK FETCH/msk_service_port_seq.xlsx
+++ b/MSK FETCH/msk_service_port_seq.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\demo\capaStudy\MSK FETCH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E009586E-4808-496A-A69C-F9CDB20061F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE2CB89-85CB-4D59-8241-6F30487B4D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5130" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D81B5631-E93A-4C80-84BC-EACFC8E297C7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{D81B5631-E93A-4C80-84BC-EACFC8E297C7}"/>
   </bookViews>
   <sheets>
     <sheet name="PortCalls" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="100">
   <si>
     <t>service</t>
   </si>
@@ -132,17 +132,9 @@
     <t>T4HWDGEKCG3L1</t>
   </si>
   <si>
-    <t>Aarhus</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>2RX5LS7KU273Y</t>
   </si>
   <si>
-    <t>Gothenburg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>148LVMHYNW4N3</t>
   </si>
   <si>
@@ -153,10 +145,6 @@
   </si>
   <si>
     <t>1YCLYW8V7RZB2</t>
-  </si>
-  <si>
-    <t>Ningbo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>AE11</t>
@@ -312,17 +300,10 @@
     <t>2XOHKM8FX8VI7</t>
   </si>
   <si>
-    <t>0C7LP1SK8P5TU</t>
-  </si>
-  <si>
     <t>Port Said East</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3I6W2NB2MQV7I</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Xingang</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -341,6 +322,48 @@
   <si>
     <t>Jeddah</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>London Gateway</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ningbo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rotterdam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tanjung Pelepas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Izmit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Istanbul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xingang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2H6OTZRVQVELZ</t>
+  </si>
+  <si>
+    <t>Port Tangier Mediterranee</t>
+  </si>
+  <si>
+    <t>Busan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jeddah</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -806,8 +829,9 @@
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
+      <c r="D2" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C2,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2IW9P6J7XAW72</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -815,13 +839,15 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
+        <f>B2+1</f>
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
+      <c r="D3" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C3,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>0L3DBFFJ3KZ9A</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -829,13 +855,15 @@
         <v>4</v>
       </c>
       <c r="B4" s="3">
+        <f t="shared" ref="B4:B8" si="0">B3+1</f>
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>10</v>
+      <c r="D4" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C4,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2DTLIHUG9YN7S</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -843,13 +871,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>12</v>
+      <c r="D5" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C5,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>1JUKNJGWHQBNJ</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -857,13 +887,15 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
+      <c r="D6" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C6,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>03KFCBH0IX2TA</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -871,27 +903,31 @@
         <v>4</v>
       </c>
       <c r="B7" s="3">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
+      <c r="D7" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C7,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>0ZBIURQPE236H</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>89</v>
+      </c>
+      <c r="D8" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C8,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>T4HWDGEKCG3L1</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -899,13 +935,14 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D9" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C9,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>104T898SJZ6GU</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -913,13 +950,15 @@
         <v>17</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <f>B9+1</f>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D10" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C10,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2IW9P6J7XAW72</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -927,13 +966,15 @@
         <v>17</v>
       </c>
       <c r="B11" s="3">
-        <v>4</v>
+        <f t="shared" ref="B11:B14" si="1">B10+1</f>
+        <v>3</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C11,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2DTLIHUG9YN7S</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -941,13 +982,15 @@
         <v>17</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C12,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>121VWEKZEDMRJ</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -955,27 +998,31 @@
         <v>17</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="D13" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C13,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>1ZPUMHQGZ3KOU</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>6</v>
+        <v>24</v>
+      </c>
+      <c r="D14" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C14,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>3EX4F5S3MB4OU</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -983,13 +1030,14 @@
         <v>26</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D15" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C15,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2IW9P6J7XAW72</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -997,13 +1045,15 @@
         <v>26</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <f>B15+1</f>
+        <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>10</v>
+        <v>90</v>
+      </c>
+      <c r="D16" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C16,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>104T898SJZ6GU</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -1011,13 +1061,15 @@
         <v>26</v>
       </c>
       <c r="B17" s="3">
-        <v>4</v>
+        <f t="shared" ref="B17:B20" si="2">B16+1</f>
+        <v>3</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>29</v>
+        <v>9</v>
+      </c>
+      <c r="D17" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C17,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2DTLIHUG9YN7S</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -1025,13 +1077,15 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
+      </c>
+      <c r="D18" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C18,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>05R47F3DBN69Q</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -1039,438 +1093,493 @@
         <v>26</v>
       </c>
       <c r="B19" s="3">
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="D19" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C19,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>T4HWDGEKCG3L1</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B20" s="3">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>36</v>
+        <v>91</v>
+      </c>
+      <c r="D20" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C20,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>1JUKNJGWHQBNJ</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="D21" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C21,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>1YCLYW8V7RZB2</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B22" s="3">
-        <v>3</v>
+        <f>B21+1</f>
+        <v>2</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
+      </c>
+      <c r="D22" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C22,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>0L3DBFFJ3KZ9A</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <f t="shared" ref="B23:B27" si="3">B22+1</f>
+        <v>3</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>29</v>
+        <v>9</v>
+      </c>
+      <c r="D23" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C23,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2DTLIHUG9YN7S</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="D24" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C24,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>T4HWDGEKCG3L1</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B25" s="3">
-        <v>6</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="D25" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C25,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>3EX4F5S3MB4OU</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B26" s="3">
-        <v>7</v>
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D26" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C26,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>03KFCBH0IX2TA</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="D27" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C27,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>1JUKNJGWHQBNJ</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B28" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D28" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C28,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2IW9P6J7XAW72</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B29" s="3">
-        <v>3</v>
+        <f>B28+1</f>
+        <v>2</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="D29" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C29,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>0L3DBFFJ3KZ9A</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B30" s="3">
-        <v>4</v>
+        <f t="shared" ref="B30:B46" si="4">B29+1</f>
+        <v>3</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="D30" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C30,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2DTLIHUG9YN7S</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B31" s="3">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>4</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="D31" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C31,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>121VWEKZEDMRJ</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B32" s="3">
-        <v>6</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="D32" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C32,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>12LNX9VI6SCYH</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="3">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3">
-        <v>7</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>44</v>
+      <c r="D33" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C33,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>1FQMCYMU9XLZ2</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B34" s="3">
-        <v>8</v>
+        <f t="shared" si="4"/>
+        <v>7</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
+      </c>
+      <c r="D34" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C34,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2743COUCZS8SF</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B35" s="3">
-        <v>9</v>
+        <f t="shared" si="4"/>
+        <v>8</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="D35" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C35,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>0KSZPEKFXG8ZJ</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A36" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>9</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>19</v>
+        <v>44</v>
+      </c>
+      <c r="D36" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C36,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2R3AZ1DW4RJB3</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A37" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B37" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D37" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C37,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>104T898SJZ6GU</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B38" s="3">
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D38" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C38,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2IW9P6J7XAW72</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B39" s="3">
-        <v>4</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>51</v>
+        <v>83</v>
+      </c>
+      <c r="D39" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C39,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>3I6W2NB2MQV7I</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="3">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B40" s="3">
-        <v>5</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>53</v>
+      <c r="D40" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C40,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2XELE43QKIMIN</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B41" s="3">
-        <v>6</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
+      </c>
+      <c r="D41" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C41,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>3RIJXP3USK909</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A42" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B42" s="3">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="D42" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C42,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>1YCLYW8V7RZB2</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A43" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B43" s="3">
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>58</v>
+        <v>90</v>
+      </c>
+      <c r="D43" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C43,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>104T898SJZ6GU</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A44" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B44" s="3">
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>19</v>
+        <v>92</v>
+      </c>
+      <c r="D44" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C44,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2DTLIHUG9YN7S</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A45" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B45" s="3">
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>10</v>
+        <v>93</v>
+      </c>
+      <c r="D45" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C45,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>02W224NQ4IGAE</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A46" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B46" s="3">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>60</v>
+        <v>94</v>
+      </c>
+      <c r="D46" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C46,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>0FC4MM5Y0O0Z2</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A47" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B47" s="3">
         <v>1</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="D47" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C47,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2H6OTZRVQVELZ</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A48" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B48" s="3">
         <v>2</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="D48" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C48,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>1YCLYW8V7RZB2</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A49" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B49" s="3">
         <v>3</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D49" s="3" t="s">
         <v>85</v>
+      </c>
+      <c r="D49" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C49,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2XOHKM8FX8VI7</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A50" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B50" s="3">
         <v>4</v>
@@ -1478,27 +1587,29 @@
       <c r="C50" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>19</v>
+      <c r="D50" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C50,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>104T898SJZ6GU</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A51" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B51" s="3">
         <v>5</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>6</v>
+        <v>86</v>
+      </c>
+      <c r="D51" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C51,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2IW9P6J7XAW72</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A52" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B52" s="3">
         <f>B51+1</f>
@@ -1507,53 +1618,57 @@
       <c r="C52" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>10</v>
+      <c r="D52" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C52,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>2DTLIHUG9YN7S</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A53" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B53" s="3">
-        <f t="shared" ref="B53:B55" si="0">B52+1</f>
+        <f t="shared" ref="B53:B55" si="5">B52+1</f>
         <v>7</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>21</v>
+        <v>87</v>
+      </c>
+      <c r="D53" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C53,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>0C29F4LWXIITO</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A54" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" s="3">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B54" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>88</v>
+      <c r="D54" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C54,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>3I6W2NB2MQV7I</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" x14ac:dyDescent="0.4">
       <c r="A55" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B55" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
+      </c>
+      <c r="D55" s="3" t="str">
+        <f>_xlfn.XLOOKUP(C55,Sheet1!$A$2:$A$100,Sheet1!$B$2:$B$100)</f>
+        <v>0NJO1NEUBFC7W</v>
       </c>
     </row>
   </sheetData>
@@ -1564,22 +1679,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106540CA-D1F6-4DD9-BD5D-9B38A673788E}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="36.53125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="9.06640625" style="5"/>
-    <col min="8" max="8" width="10.19921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="5"/>
+    <col min="3" max="5" width="9.06640625" style="5"/>
+    <col min="6" max="6" width="10.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.06640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.5">
@@ -1640,10 +1755,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.5">
@@ -1672,170 +1787,202 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A26" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A27" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A28" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A29" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A30" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A32" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A33" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A35" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A36" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A37" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
